--- a/output/pdf_financials_xlsx/BHC.xlsx
+++ b/output/pdf_financials_xlsx/BHC.xlsx
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1800.2</v>
+        <v>1980.7</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2179.4</v>
+        <v>2331</v>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
@@ -4028,16 +4028,16 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>3227</v>
+        <v>3285</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3694</v>
+        <v>3903</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>3197</v>
+        <v>3425</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>4511</v>
+        <v>5745</v>
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>-132.8</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-915.9</v>
+        <v>-1831.8</v>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">

--- a/output/pdf_financials_xlsx/BHC.xlsx
+++ b/output/pdf_financials_xlsx/BHC.xlsx
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1667,28 +1667,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-394.2</v>
+        <v>-400.2</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1314.4</v>
+        <v>-1322.4</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1092.6</v>
+        <v>1087.6</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-443</v>
+        <v>-447</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-4843</v>
+        <v>-4851</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-8298</v>
+        <v>-8309</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3620</v>
+        <v>-3632</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1759,28 +1759,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-394.2</v>
+        <v>-400.2</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1314.4</v>
+        <v>-1322.4</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1092.6</v>
+        <v>1087.6</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-443</v>
+        <v>-447</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4843</v>
+        <v>-4851</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-8298</v>
+        <v>-8309</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3620</v>
+        <v>-3632</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1805,28 +1805,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-11.32628433513389</v>
+        <v>-11.4986783128376</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-22.78147531891292</v>
+        <v>-22.92013311148087</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>13.31464781866927</v>
+        <v>13.25371679259079</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-4.240451804345746</v>
+        <v>-4.278740308222456</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-50.06202191440976</v>
+        <v>-50.14471780028944</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>7.599724896836315</v>
+        <v>7.462173314993123</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-99.02147971360382</v>
+        <v>-99.1527446300716</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-42.08812928729218</v>
+        <v>-42.22764794791303</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>343.4</v>
+        <v>3285.6</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>641.9</v>
+        <v>3870.5</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -2666,16 +2666,16 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>696</v>
+        <v>4535</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>771</v>
+        <v>4026</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>689</v>
+        <v>3490</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>779</v>
+        <v>3726</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
@@ -3728,16 +3728,16 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0</v>
+        <v>29845</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0</v>
+        <v>25235</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0</v>
+        <v>24077</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0</v>
+        <v>24661</v>
       </c>
       <c r="J69" s="1" t="inlineStr">
         <is>
@@ -3828,16 +3828,16 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>29845</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>25235</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>24077</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>24661</v>
       </c>
       <c r="J71" s="1" t="inlineStr">
         <is>
@@ -4028,16 +4028,16 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>3285</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3903</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>3425</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>5745</v>
+        <v>0</v>
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
@@ -4128,16 +4128,16 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>29845</v>
+        <v>0</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>25235</v>
+        <v>0</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>24077</v>
+        <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>24661</v>
+        <v>0</v>
       </c>
       <c r="J77" s="1" t="inlineStr">
         <is>
@@ -4228,16 +4228,16 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>29845</v>
+        <v>0</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>25235</v>
+        <v>0</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>24077</v>
+        <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>24661</v>
+        <v>0</v>
       </c>
       <c r="J79" s="1" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -35381,7 +35381,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E420" s="5" t="n">
@@ -35442,7 +35442,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E421" s="5" t="n">

--- a/output/pdf_financials_xlsx/BHC.xlsx
+++ b/output/pdf_financials_xlsx/BHC.xlsx
@@ -1722,19 +1722,19 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>2257</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>2673</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>2690</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>2644</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>1897</v>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         <v>1087.6</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-447</v>
+        <v>1810</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4851</v>
+        <v>-2178</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>651</v>
+        <v>3341</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-8309</v>
+        <v>-5665</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3632</v>
+        <v>-1735</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1814,19 +1814,19 @@
         <v>13.25371679259079</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-4.278740308222456</v>
+        <v>17.32554800421174</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-50.14471780028944</v>
+        <v>-22.51395493074219</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>7.462173314993123</v>
+        <v>38.29665291150848</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-99.1527446300716</v>
+        <v>-67.60143198090692</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-42.22764794791303</v>
+        <v>-20.17207301476573</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -5224,19 +5224,19 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>2467</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2866</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>2858</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2819</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2075</v>
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
@@ -23141,7 +23141,11 @@
           <t>Depreciation and amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -34932,7 +34936,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">

--- a/output/pdf_financials_xlsx/BHC.xlsx
+++ b/output/pdf_financials_xlsx/BHC.xlsx
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>2073</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>2288.4</v>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
@@ -3078,16 +3078,16 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>2508</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>2833</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>2875</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>3107</v>
       </c>
       <c r="J56" s="1" t="inlineStr">
         <is>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>838.8</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>977.9</v>
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
@@ -3128,16 +3128,16 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>1196</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>1430</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>1522</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>1641</v>
       </c>
       <c r="J57" s="1" t="inlineStr">
         <is>
@@ -5353,28 +5353,28 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>121.5</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-110.3</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-72</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
@@ -5491,28 +5491,28 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-80.3</v>
+        <v>-69.09999999999999</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-122.7</v>
+        <v>-1.2</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-174.3</v>
+        <v>-284.6</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-276</v>
+        <v>-367</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-164</v>
+        <v>68</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-5</v>
+        <v>-77</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-209</v>
+        <v>-208</v>
       </c>
       <c r="J106" s="1" t="inlineStr">
         <is>
@@ -5862,25 +5862,25 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-18.2</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J114" s="1" t="inlineStr">
         <is>
@@ -5914,19 +5914,19 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J115" s="1" t="inlineStr">
         <is>
@@ -6181,16 +6181,16 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-280.7</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-55.6</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-72</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -24320,7 +24320,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E255" s="5" t="n">
         <v>11.2</v>
       </c>
@@ -24672,7 +24676,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -24735,7 +24743,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -26610,7 +26622,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E291" s="5" t="n">
         <v>-116</v>
       </c>
@@ -27081,7 +27097,11 @@
           <t>Repurchases of common shares</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E298" s="5" t="n">
         <v>-280.7</v>
       </c>
@@ -28816,7 +28836,11 @@
           <t>Prepaid expenses and other current assets (90.6)</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -29453,7 +29477,11 @@
           <t>Purchases of marketable securities (49.3)</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -30295,7 +30323,11 @@
           <t>Repurchases of common shares (72.4)</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
